--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -790,7 +790,7 @@
     <t>Specimen.collection.method</t>
   </si>
   <si>
-    <t>Technique used to perform collection</t>
+    <t>Actes de prélèvement</t>
   </si>
   <si>
     <t>A coded value specifying the technique that is used to perform the procedure.</t>
@@ -884,14 +884,7 @@
     <t>Specimen.processing.description</t>
   </si>
   <si>
-    <t>Acte de prélèvement :
-Pour un prélèvement en vue d'examen de biologie médicale, le code affiné NABM de l'acte de prélèvement doit être renseigné si connu, sauf dans le cas d'un recueil d'échantillon effectué par le patient lui-même.
-Un prélèvement cytologique ou de tissu en vue d'un examen d'anatomie ou de cytologie pathologiques est codé à l'aide d'une nomenclature précisée dans les modèles de contenus métiers.
-Par défaut, utiliser le code suivant :
-code='33882-2'
-displayName='Prélèvement'
-codeSystem='2.16.840.1.113883.6.1'
-codeSystemName='LOINC'</t>
+    <t>Textual description of procedure</t>
   </si>
   <si>
     <t>Textual description of procedure.</t>
@@ -913,195 +906,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.id</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding.id</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding.extension</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding.code</t>
-  </si>
-  <si>
-    <t>Acte de prélèvement</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
@@ -1604,11 +1408,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.6953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.6953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.40234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.40234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1635,7 +1439,7 @@
     <col min="26" max="26" width="52.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="31.46875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2763,7 +2567,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -2776,13 +2580,13 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>76</v>
@@ -3643,7 +3447,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>202</v>
       </c>
@@ -3662,7 +3466,7 @@
         <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>76</v>
@@ -5512,7 +5316,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>286</v>
       </c>
@@ -5528,10 +5332,10 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>76</v>
@@ -5540,13 +5344,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5597,47 +5401,47 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>212</v>
+        <v>286</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>76</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5649,17 +5453,15 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>131</v>
+        <v>230</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>132</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5696,34 +5498,34 @@
         <v>76</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>288</v>
+        <v>76</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>289</v>
+        <v>76</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>290</v>
+        <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5732,12 +5534,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5751,29 +5553,25 @@
         <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
       </c>
@@ -5821,7 +5619,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5842,15 +5640,15 @@
         <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>299</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5956,10 +5754,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6029,16 +5827,16 @@
         <v>76</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>288</v>
+        <v>76</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>289</v>
+        <v>76</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>290</v>
+        <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>216</v>
@@ -6067,45 +5865,45 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>219</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>304</v>
+        <v>220</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>305</v>
+        <v>134</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>306</v>
+        <v>140</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -6154,36 +5952,36 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>221</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>308</v>
+        <v>128</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>309</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6194,7 +5992,7 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>76</v>
@@ -6206,17 +6004,15 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6265,13 +6061,13 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>76</v>
@@ -6280,21 +6076,21 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>315</v>
+        <v>146</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6302,33 +6098,31 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
       </c>
@@ -6376,7 +6170,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6391,21 +6185,21 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>323</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6413,33 +6207,31 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>327</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
       </c>
@@ -6463,13 +6255,13 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>76</v>
+        <v>313</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>76</v>
+        <v>314</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
@@ -6487,7 +6279,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6502,21 +6294,21 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>329</v>
+        <v>171</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6536,23 +6328,19 @@
         <v>76</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>332</v>
+        <v>241</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
       </c>
@@ -6600,7 +6388,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6615,21 +6403,21 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>339</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6649,23 +6437,19 @@
         <v>76</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
       </c>
@@ -6713,7 +6497,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6728,21 +6512,21 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>347</v>
+        <v>325</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6753,10 +6537,10 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>76</v>
@@ -6765,13 +6549,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6798,13 +6582,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>76</v>
+        <v>330</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>76</v>
+        <v>331</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6822,13 +6606,13 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
@@ -6837,21 +6621,21 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6862,7 +6646,7 @@
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -6871,19 +6655,23 @@
         <v>76</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
       </c>
@@ -6907,13 +6695,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>76</v>
+        <v>339</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>76</v>
+        <v>340</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6931,13 +6719,13 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>76</v>
@@ -6946,21 +6734,21 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6974,7 +6762,7 @@
         <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>76</v>
@@ -6983,13 +6771,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>343</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>358</v>
+        <v>50</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7040,7 +6828,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7055,1226 +6843,17 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>408</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM60">
+  <autoFilter ref="A1:AM49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8284,7 +6863,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
